--- a/cloudflare-deploy/public/library/student/student-kr.xlsx
+++ b/cloudflare-deploy/public/library/student/student-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2596,6 +2596,60 @@
       <c r="E53" s="20" t="inlineStr">
         <is>
           <t>학교 일정이 있는 요일은 피해서 고르세요. 나중에 바꾸는 것보다 처음에 잘 고르는 게 편해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="54" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>구조 항해 (망고 구조선의 대항해)</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🌊 구조 항해를 열어요. → English(영어) / 中文(중국어) 모드를 고르고 출항! Start를 눌러요. → 바다에 빠진 단어 친구를 향해 배를 몰아 건져 올려요. → 상어·거북이·돌고래는 부딪히지 않게 피해요. → 구조가 끝나면 문장 따라 말하기 미션에 도전해요.</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>구조한 단어로 나오는 문장 미션이 진짜 복습이에요. 소리 내어 또박또박 따라 하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>[학부모] 오각형 월간 성적표</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>카카오톡으로 받은 성적표 링크를 열어요. → 맨 위 오각형 그래프로 다섯 가지 힘의 균형을 확인해요. → 이번 기간 현황(출석·판단력)과 담임의 한마디를 읽어요. → 가정에서 도와주실 수 있어요 팁을 참고해요. → 종이로 보관하려면 위쪽 🖨 인쇄/PDF를 눌러요.</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>오각형이 고르게 클수록 균형 잡힌 학습이에요. 움푹 들어간 축이 이번 달 도전 과제예요.</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F588"/>
+  <dimension ref="A1:F616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9143,8 +9197,324 @@
       <c r="E588" s="33" t="n"/>
       <c r="F588" s="33" t="n"/>
     </row>
+    <row r="590" ht="26" customHeight="1">
+      <c r="A590" s="21" t="inlineStr">
+        <is>
+          <t>51  🌊 구조 항해 (망고 구조선의 대항해)  —  바다 친구를 구하며 단어를 익혀요</t>
+        </is>
+      </c>
+      <c r="B590" s="22" t="n"/>
+      <c r="C590" s="22" t="n"/>
+      <c r="D590" s="22" t="n"/>
+      <c r="E590" s="22" t="n"/>
+      <c r="F590" s="22" t="n"/>
+    </row>
+    <row r="591" ht="42" customHeight="1">
+      <c r="A591" s="23" t="inlineStr">
+        <is>
+          <t>📖 폭풍에 휩쓸려 바다에 빠진 단어 친구들을 배로 건져 올리는 게임이에요. 친구를 구하면 원어민 발음과 뜻이 공개되고, 중간에 나타나는 상어·거북이·돌고래 같은 바다 생물은 피해야 해요. 시간 안에 최대한 많이 구조한 뒤, 배운 단어로 만든 문장을 듣고 따라 말하기 미션까지 이어져요.</t>
+        </is>
+      </c>
+      <c r="B591" s="24" t="n"/>
+      <c r="C591" s="24" t="n"/>
+      <c r="D591" s="24" t="n"/>
+      <c r="E591" s="24" t="n"/>
+      <c r="F591" s="24" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B592" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="30" customHeight="1">
+      <c r="A593" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B593" s="28" t="inlineStr">
+        <is>
+          <t>학습 게임 허브에서 🌊 구조 항해를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="30" customHeight="1">
+      <c r="A594" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B594" s="28" t="inlineStr">
+        <is>
+          <t>English(영어) / 中文(중국어) 모드를 고르고 출항! Start를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="30" customHeight="1">
+      <c r="A595" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B595" s="28" t="inlineStr">
+        <is>
+          <t>바다에 빠진 단어 친구를 향해 배를 몰아 건져 올려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="30" customHeight="1">
+      <c r="A596" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B596" s="28" t="inlineStr">
+        <is>
+          <t>상어·거북이·돌고래는 부딪히지 않게 피해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="30" customHeight="1">
+      <c r="A597" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B597" s="28" t="inlineStr">
+        <is>
+          <t>구조가 끝나면 문장 따라 말하기 미션에 도전해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="24" customHeight="1">
+      <c r="A598" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B598" s="30" t="inlineStr">
+        <is>
+          <t>친구를 구할 때마다 원어민 발음이 들려 듣기 연습이 돼요.</t>
+        </is>
+      </c>
+      <c r="C598" s="31" t="n"/>
+      <c r="D598" s="31" t="n"/>
+      <c r="E598" s="31" t="n"/>
+      <c r="F598" s="31" t="n"/>
+    </row>
+    <row r="599" ht="24" customHeight="1">
+      <c r="A599" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B599" s="30" t="inlineStr">
+        <is>
+          <t>영어·중국어 두 모드를 같은 방식으로 즐길 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C599" s="31" t="n"/>
+      <c r="D599" s="31" t="n"/>
+      <c r="E599" s="31" t="n"/>
+      <c r="F599" s="31" t="n"/>
+    </row>
+    <row r="600" ht="24" customHeight="1">
+      <c r="A600" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B600" s="30" t="inlineStr">
+        <is>
+          <t>실사에 가까운 바다 생물이 등장해 몰입감이 높아요.</t>
+        </is>
+      </c>
+      <c r="C600" s="31" t="n"/>
+      <c r="D600" s="31" t="n"/>
+      <c r="E600" s="31" t="n"/>
+      <c r="F600" s="31" t="n"/>
+    </row>
+    <row r="601" ht="26" customHeight="1">
+      <c r="A601" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 움직임이 많은 게임이에요. 저사양 기기에서 느리면 잠시 쉬었다 해 주세요.</t>
+        </is>
+      </c>
+      <c r="B601" s="35" t="n"/>
+      <c r="C601" s="35" t="n"/>
+      <c r="D601" s="35" t="n"/>
+      <c r="E601" s="35" t="n"/>
+      <c r="F601" s="35" t="n"/>
+    </row>
+    <row r="602" ht="30" customHeight="1">
+      <c r="A602" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 구조한 단어로 나오는 문장 미션이 진짜 복습이에요. 소리 내어 또박또박 따라 하세요.</t>
+        </is>
+      </c>
+      <c r="B602" s="33" t="n"/>
+      <c r="C602" s="33" t="n"/>
+      <c r="D602" s="33" t="n"/>
+      <c r="E602" s="33" t="n"/>
+      <c r="F602" s="33" t="n"/>
+    </row>
+    <row r="604" ht="26" customHeight="1">
+      <c r="A604" s="21" t="inlineStr">
+        <is>
+          <t>52  🌟 [학부모] 오각형 월간 성적표  —  5가지 힘을 한눈에 · 인쇄도 한 번에</t>
+        </is>
+      </c>
+      <c r="B604" s="22" t="n"/>
+      <c r="C604" s="22" t="n"/>
+      <c r="D604" s="22" t="n"/>
+      <c r="E604" s="22" t="n"/>
+      <c r="F604" s="22" t="n"/>
+    </row>
+    <row r="605" ht="42" customHeight="1">
+      <c r="A605" s="23" t="inlineStr">
+        <is>
+          <t>📖 자녀의 한 달 학습을 오각형 그래프 다섯 축으로 한눈에 보여 주는 성적표예요. 발음·유창성 / 어휘 수준 / 문장 구성력 / 수업 태도 / 학습 참여도 를 그래프로 보고, 출결·판단력 지수·담임의 한마디까지 이어져요. 위쪽 인쇄/PDF 버튼으로 그대로 출력하거나 파일로 저장할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B605" s="24" t="n"/>
+      <c r="C605" s="24" t="n"/>
+      <c r="D605" s="24" t="n"/>
+      <c r="E605" s="24" t="n"/>
+      <c r="F605" s="24" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B606" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="30" customHeight="1">
+      <c r="A607" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B607" s="28" t="inlineStr">
+        <is>
+          <t>카카오톡으로 받은 성적표 링크를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="30" customHeight="1">
+      <c r="A608" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B608" s="28" t="inlineStr">
+        <is>
+          <t>맨 위 오각형 그래프로 다섯 가지 힘의 균형을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="30" customHeight="1">
+      <c r="A609" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B609" s="28" t="inlineStr">
+        <is>
+          <t>이번 기간 현황(출석·판단력)과 담임의 한마디를 읽어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="30" customHeight="1">
+      <c r="A610" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B610" s="28" t="inlineStr">
+        <is>
+          <t>가정에서 도와주실 수 있어요 팁을 참고해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="30" customHeight="1">
+      <c r="A611" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B611" s="28" t="inlineStr">
+        <is>
+          <t>종이로 보관하려면 위쪽 🖨 인쇄/PDF를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="24" customHeight="1">
+      <c r="A612" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B612" s="30" t="inlineStr">
+        <is>
+          <t>점수가 실제로 쌓인 축만 채워져요 — 지어낸 숫자는 없어요.</t>
+        </is>
+      </c>
+      <c r="C612" s="31" t="n"/>
+      <c r="D612" s="31" t="n"/>
+      <c r="E612" s="31" t="n"/>
+      <c r="F612" s="31" t="n"/>
+    </row>
+    <row r="613" ht="24" customHeight="1">
+      <c r="A613" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B613" s="30" t="inlineStr">
+        <is>
+          <t>2개월에 한 번 정리되어 변화 흐름을 보기 좋아요.</t>
+        </is>
+      </c>
+      <c r="C613" s="31" t="n"/>
+      <c r="D613" s="31" t="n"/>
+      <c r="E613" s="31" t="n"/>
+      <c r="F613" s="31" t="n"/>
+    </row>
+    <row r="614" ht="24" customHeight="1">
+      <c r="A614" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B614" s="30" t="inlineStr">
+        <is>
+          <t>한 화면에 다 담겨 인쇄 한 장으로 끝나요.</t>
+        </is>
+      </c>
+      <c r="C614" s="31" t="n"/>
+      <c r="D614" s="31" t="n"/>
+      <c r="E614" s="31" t="n"/>
+      <c r="F614" s="31" t="n"/>
+    </row>
+    <row r="615" ht="26" customHeight="1">
+      <c r="A615" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 성적표는 학습 기록이 쌓여야 채워져요. 기록이 적은 달은 일부 축이 비어 보일 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B615" s="35" t="n"/>
+      <c r="C615" s="35" t="n"/>
+      <c r="D615" s="35" t="n"/>
+      <c r="E615" s="35" t="n"/>
+      <c r="F615" s="35" t="n"/>
+    </row>
+    <row r="616" ht="30" customHeight="1">
+      <c r="A616" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 오각형이 고르게 클수록 균형 잡힌 학습이에요. 움푹 들어간 축이 이번 달 도전 과제예요.</t>
+        </is>
+      </c>
+      <c r="B616" s="33" t="n"/>
+      <c r="C616" s="33" t="n"/>
+      <c r="D616" s="33" t="n"/>
+      <c r="E616" s="33" t="n"/>
+      <c r="F616" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="538">
+  <mergeCells count="564">
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B445:F445"/>
@@ -9165,6 +9535,7 @@
     <mergeCell ref="A274:F274"/>
     <mergeCell ref="A372:F372"/>
     <mergeCell ref="B515:F515"/>
+    <mergeCell ref="A605:F605"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A549:F549"/>
@@ -9200,6 +9571,7 @@
     <mergeCell ref="B446:F446"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A435:F435"/>
+    <mergeCell ref="B609:F609"/>
     <mergeCell ref="A362:F362"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
@@ -9232,6 +9604,7 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B249:F249"/>
     <mergeCell ref="A510:F510"/>
+    <mergeCell ref="B599:F599"/>
     <mergeCell ref="A295:F295"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A334:F334"/>
@@ -9241,6 +9614,7 @@
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="B327:F327"/>
     <mergeCell ref="B454:F454"/>
+    <mergeCell ref="B612:F612"/>
     <mergeCell ref="A365:F365"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B93:F93"/>
@@ -9273,6 +9647,7 @@
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B277:F277"/>
+    <mergeCell ref="B600:F600"/>
     <mergeCell ref="B404:F404"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B81:F81"/>
@@ -9341,6 +9716,7 @@
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A282:F282"/>
+    <mergeCell ref="B596:F596"/>
     <mergeCell ref="B571:F571"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
@@ -9388,11 +9764,14 @@
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="B337:F337"/>
     <mergeCell ref="B579:F579"/>
+    <mergeCell ref="B610:F610"/>
+    <mergeCell ref="B597:F597"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="B339:F339"/>
     <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A615:F615"/>
     <mergeCell ref="B501:F501"/>
     <mergeCell ref="A485:F485"/>
     <mergeCell ref="B526:F526"/>
@@ -9413,12 +9792,14 @@
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B465:F465"/>
     <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B592:F592"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B431:F431"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B287:F287"/>
     <mergeCell ref="B358:F358"/>
     <mergeCell ref="B529:F529"/>
+    <mergeCell ref="B594:F594"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
@@ -9432,6 +9813,7 @@
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B384:F384"/>
     <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B607:F607"/>
     <mergeCell ref="A422:F422"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B442:F442"/>
@@ -9455,12 +9837,15 @@
     <mergeCell ref="B520:F520"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B593:F593"/>
     <mergeCell ref="B397:F397"/>
     <mergeCell ref="B360:F360"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="B239:F239"/>
     <mergeCell ref="B310:F310"/>
+    <mergeCell ref="B608:F608"/>
+    <mergeCell ref="B595:F595"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B361:F361"/>
@@ -9477,11 +9862,13 @@
     <mergeCell ref="A203:F203"/>
     <mergeCell ref="B542:F542"/>
     <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B613:F613"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
     <mergeCell ref="B514:F514"/>
     <mergeCell ref="B452:F452"/>
+    <mergeCell ref="B606:F606"/>
     <mergeCell ref="B544:F544"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="B258:F258"/>
@@ -9518,7 +9905,9 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B440:F440"/>
     <mergeCell ref="B240:F240"/>
+    <mergeCell ref="B611:F611"/>
     <mergeCell ref="A234:F234"/>
+    <mergeCell ref="B598:F598"/>
     <mergeCell ref="B377:F377"/>
     <mergeCell ref="A211:F211"/>
     <mergeCell ref="B329:F329"/>
@@ -9526,6 +9915,7 @@
     <mergeCell ref="A275:F275"/>
     <mergeCell ref="B316:F316"/>
     <mergeCell ref="B565:F565"/>
+    <mergeCell ref="B614:F614"/>
     <mergeCell ref="A511:F511"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B266:F266"/>
@@ -9552,7 +9942,10 @@
     <mergeCell ref="A587:F587"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A524:F524"/>
+    <mergeCell ref="A616:F616"/>
+    <mergeCell ref="A601:F601"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A591:F591"/>
     <mergeCell ref="A224:F224"/>
     <mergeCell ref="A588:F588"/>
     <mergeCell ref="A72:F72"/>
@@ -9602,6 +9995,7 @@
     <mergeCell ref="B269:F269"/>
     <mergeCell ref="A403:F403"/>
     <mergeCell ref="B187:F187"/>
+    <mergeCell ref="A590:F590"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B556:F556"/>
@@ -9650,10 +10044,12 @@
     <mergeCell ref="B206:F206"/>
     <mergeCell ref="A233:F233"/>
     <mergeCell ref="B66:F66"/>
+    <mergeCell ref="A602:F602"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="A533:F533"/>
+    <mergeCell ref="A604:F604"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
     <mergeCell ref="A483:F483"/>
